--- a/salidas/empresas/RTX.xlsx
+++ b/salidas/empresas/RTX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>22.95645904541016</v>
+        <v>22.95646858215332</v>
       </c>
       <c r="C2" t="n">
         <v>36.73379516601562</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>23.09499359130859</v>
+        <v>23.09499931335449</v>
       </c>
       <c r="C3" t="n">
         <v>36.81560516357422</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>22.8857536315918</v>
+        <v>22.8857593536377</v>
       </c>
       <c r="C4" t="n">
         <v>36.48206329345703</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>24.79653167724609</v>
+        <v>24.79653358459473</v>
       </c>
       <c r="C5" t="n">
         <v>39.52800369262695</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>24.78278350830078</v>
+        <v>24.78279113769531</v>
       </c>
       <c r="C6" t="n">
         <v>39.34550094604492</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>25.13953971862793</v>
+        <v>25.1395435333252</v>
       </c>
       <c r="C7" t="n">
         <v>39.91189575195312</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>24.65197372436523</v>
+        <v>24.6519775390625</v>
       </c>
       <c r="C8" t="n">
         <v>39.13782119750977</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>24.96651458740234</v>
+        <v>24.96650123596191</v>
       </c>
       <c r="C9" t="n">
         <v>39.46507263183594</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>25.22130012512207</v>
+        <v>25.2213020324707</v>
       </c>
       <c r="C10" t="n">
         <v>39.86783981323242</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>26.16486930847168</v>
+        <v>26.16486358642578</v>
       </c>
       <c r="C11" t="n">
         <v>41.35934448242188</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>25.79528045654297</v>
+        <v>25.79528427124023</v>
       </c>
       <c r="C12" t="n">
         <v>40.61044692993164</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>24.9918041229248</v>
+        <v>24.99180793762207</v>
       </c>
       <c r="C13" t="n">
         <v>39.34550094604492</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>27.19037818908691</v>
+        <v>27.19038200378418</v>
       </c>
       <c r="C14" t="n">
         <v>42.80679702758789</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>26.34288024902344</v>
+        <v>26.34288597106934</v>
       </c>
       <c r="C15" t="n">
         <v>41.30899810791016</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>26.94084739685059</v>
+        <v>26.94084548950195</v>
       </c>
       <c r="C17" t="n">
         <v>42.24669647216797</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>28.42334747314453</v>
+        <v>28.42333793640137</v>
       </c>
       <c r="C18" t="n">
         <v>44.39899444580078</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>28.57642936706543</v>
+        <v>28.57643890380859</v>
       </c>
       <c r="C19" t="n">
         <v>44.63813781738281</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>29.39831924438477</v>
+        <v>29.39831352233887</v>
       </c>
       <c r="C20" t="n">
         <v>45.92196273803711</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>30.19988441467285</v>
+        <v>30.19987678527832</v>
       </c>
       <c r="C21" t="n">
         <v>46.96664428710938</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>32.5671501159668</v>
+        <v>32.56715393066406</v>
       </c>
       <c r="C22" t="n">
         <v>50.6482048034668</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>30.99301910400391</v>
+        <v>30.99300956726074</v>
       </c>
       <c r="C23" t="n">
         <v>48.20012664794922</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>30.38559913635254</v>
+        <v>30.3856086730957</v>
       </c>
       <c r="C24" t="n">
         <v>47.05475234985352</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>31.10491752624512</v>
+        <v>31.10490798950195</v>
       </c>
       <c r="C25" t="n">
         <v>48.16865921020508</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>29.77603912353516</v>
+        <v>29.77602005004883</v>
       </c>
       <c r="C26" t="n">
         <v>46.11075973510742</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>28.78086471557617</v>
+        <v>28.7808780670166</v>
       </c>
       <c r="C27" t="n">
         <v>44.37382125854492</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>29.12158966064453</v>
+        <v>29.1215934753418</v>
       </c>
       <c r="C30" t="n">
         <v>44.70736312866211</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>25.29282569885254</v>
+        <v>25.29281997680664</v>
       </c>
       <c r="C31" t="n">
         <v>38.82945251464844</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>26.22746658325195</v>
+        <v>26.22747230529785</v>
       </c>
       <c r="C32" t="n">
         <v>40.26431655883789</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>27.01745414733887</v>
+        <v>27.0174446105957</v>
       </c>
       <c r="C33" t="n">
         <v>41.27753448486328</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.73956108093262</v>
+        <v>24.73955917358398</v>
       </c>
       <c r="C34" t="n">
         <v>37.79735565185547</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>22.63880157470703</v>
+        <v>22.6388111114502</v>
       </c>
       <c r="C35" t="n">
         <v>34.58779144287109</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.13988876342773</v>
+        <v>20.1398868560791</v>
       </c>
       <c r="C36" t="n">
         <v>30.54122161865234</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>22.24392700195312</v>
+        <v>22.24393272399902</v>
       </c>
       <c r="C37" t="n">
         <v>33.73190689086914</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>17.08842086791992</v>
+        <v>17.08842277526855</v>
       </c>
       <c r="C39" t="n">
         <v>25.69540596008301</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>17.98824691772461</v>
+        <v>17.98826026916504</v>
       </c>
       <c r="C40" t="n">
         <v>27.04845809936523</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.44081497192383</v>
+        <v>20.44080352783203</v>
       </c>
       <c r="C41" t="n">
         <v>30.73631286621094</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>22.18027687072754</v>
+        <v>22.18027496337891</v>
       </c>
       <c r="C42" t="n">
         <v>33.1088752746582</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.96443748474121</v>
+        <v>22.96443939208984</v>
       </c>
       <c r="C44" t="n">
         <v>34.27942276000977</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>25.19680786132812</v>
+        <v>25.19681358337402</v>
       </c>
       <c r="C45" t="n">
         <v>37.35682678222656</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>25.86323738098145</v>
+        <v>25.86323356628418</v>
       </c>
       <c r="C46" t="n">
         <v>38.34487152099609</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>26.08396148681641</v>
+        <v>26.08396530151367</v>
       </c>
       <c r="C47" t="n">
         <v>38.672119140625</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>28.69967269897461</v>
+        <v>28.69967842102051</v>
       </c>
       <c r="C48" t="n">
         <v>42.31592178344727</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>29.62588310241699</v>
+        <v>29.62587928771973</v>
       </c>
       <c r="C49" t="n">
         <v>43.68156051635742</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>28.80210876464844</v>
+        <v>28.80211639404297</v>
       </c>
       <c r="C50" t="n">
         <v>42.46696090698242</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>29.49045753479004</v>
+        <v>29.49045372009277</v>
       </c>
       <c r="C51" t="n">
         <v>43.20327377319336</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>31.62116432189941</v>
+        <v>31.62115669250488</v>
       </c>
       <c r="C52" t="n">
         <v>46.32473373413086</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>32.19680404663086</v>
+        <v>32.19678115844727</v>
       </c>
       <c r="C53" t="n">
         <v>47.16802978515625</v>
@@ -1530,7 +1542,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>28.04681777954102</v>
+        <v>28.04682731628418</v>
       </c>
       <c r="C55" t="n">
         <v>40.84959030151367</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>30.72146415710449</v>
+        <v>30.72146224975586</v>
       </c>
       <c r="C56" t="n">
         <v>44.74512481689453</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>28.34732246398926</v>
+        <v>28.34732627868652</v>
       </c>
       <c r="C57" t="n">
         <v>41.03838729858398</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>30.96426773071289</v>
+        <v>30.96427917480469</v>
       </c>
       <c r="C58" t="n">
         <v>44.82693481445312</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>32.50314331054688</v>
+        <v>32.50313186645508</v>
       </c>
       <c r="C59" t="n">
         <v>47.05475234985352</v>
@@ -1680,7 +1692,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>34.4174690246582</v>
+        <v>34.41748809814453</v>
       </c>
       <c r="C61" t="n">
         <v>49.54059219360352</v>
@@ -1730,7 +1742,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>36.70855712890625</v>
+        <v>36.70853805541992</v>
       </c>
       <c r="C63" t="n">
         <v>52.57394790649414</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>37.19628524780273</v>
+        <v>37.19628143310547</v>
       </c>
       <c r="C64" t="n">
         <v>53.27249908447266</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>39.36259460449219</v>
+        <v>39.36258316040039</v>
       </c>
       <c r="C65" t="n">
         <v>56.37508010864258</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>38.77920532226562</v>
+        <v>38.77920150756836</v>
       </c>
       <c r="C66" t="n">
         <v>55.23599624633789</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>39.10615921020508</v>
+        <v>39.10616683959961</v>
       </c>
       <c r="C67" t="n">
         <v>55.70169830322266</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>36.60099411010742</v>
+        <v>36.60101318359375</v>
       </c>
       <c r="C68" t="n">
         <v>52.13341522216797</v>
@@ -1929,7 +1941,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>31.29404258728027</v>
+        <v>31.29403877258301</v>
       </c>
       <c r="C70" t="n">
         <v>44.27942276000977</v>
@@ -1987,7 +1999,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2016,7 +2028,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>32.70616149902344</v>
+        <v>32.70614242553711</v>
       </c>
       <c r="C73" t="n">
         <v>45.99748229980469</v>
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>35.05989074707031</v>
+        <v>35.05989456176758</v>
       </c>
       <c r="C74" t="n">
         <v>49.3077392578125</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>37.74402618408203</v>
+        <v>37.74402236938477</v>
       </c>
       <c r="C75" t="n">
         <v>52.78162384033203</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>37.32550048828125</v>
+        <v>37.32548522949219</v>
       </c>
       <c r="C76" t="n">
         <v>52.19635009765625</v>
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>36.74044799804688</v>
+        <v>36.74044036865234</v>
       </c>
       <c r="C77" t="n">
         <v>51.37822341918945</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>33.563232421875</v>
+        <v>33.56322860717773</v>
       </c>
       <c r="C78" t="n">
         <v>46.63939666748047</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>34.2063102722168</v>
+        <v>34.20631790161133</v>
       </c>
       <c r="C79" t="n">
         <v>47.53303909301758</v>
@@ -2248,7 +2260,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>36.41323852539062</v>
+        <v>36.41325759887695</v>
       </c>
       <c r="C81" t="n">
         <v>50.25173187255859</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>35.70186233520508</v>
+        <v>35.70185470581055</v>
       </c>
       <c r="C82" t="n">
         <v>49.26998138427734</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>35.6425666809082</v>
+        <v>35.64257049560547</v>
       </c>
       <c r="C83" t="n">
         <v>49.18816757202148</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>36.78740310668945</v>
+        <v>36.78741836547852</v>
       </c>
       <c r="C84" t="n">
         <v>50.41535568237305</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>37.659912109375</v>
+        <v>37.65991973876953</v>
       </c>
       <c r="C85" t="n">
         <v>51.61107635498047</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>40.21311950683594</v>
+        <v>40.21313095092773</v>
       </c>
       <c r="C86" t="n">
         <v>55.11013031005859</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>41.83027648925781</v>
+        <v>41.83028793334961</v>
       </c>
       <c r="C87" t="n">
         <v>56.98552322387695</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>43.16072845458984</v>
+        <v>43.16072463989258</v>
       </c>
       <c r="C88" t="n">
         <v>58.7979850769043</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>42.17213821411133</v>
+        <v>42.17214202880859</v>
       </c>
       <c r="C89" t="n">
         <v>57.45122528076172</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>44.08567810058594</v>
+        <v>44.08567047119141</v>
       </c>
       <c r="C90" t="n">
         <v>59.72309494018555</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>43.17515563964844</v>
+        <v>43.17516708374023</v>
       </c>
       <c r="C91" t="n">
         <v>58.48961639404297</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>49.04241561889648</v>
+        <v>49.04241180419922</v>
       </c>
       <c r="C92" t="n">
         <v>66.43801116943359</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>46.73543548583984</v>
+        <v>46.73543167114258</v>
       </c>
       <c r="C93" t="n">
         <v>62.9955940246582</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>50.33980941772461</v>
+        <v>50.33981323242188</v>
       </c>
       <c r="C94" t="n">
         <v>67.85399627685547</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>49.60679244995117</v>
+        <v>49.60678482055664</v>
       </c>
       <c r="C95" t="n">
         <v>66.86595153808594</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>52.04492950439453</v>
+        <v>52.04493713378906</v>
       </c>
       <c r="C96" t="n">
         <v>69.76715087890625</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>53.42515563964844</v>
+        <v>53.4251594543457</v>
       </c>
       <c r="C97" t="n">
         <v>71.61737060546875</v>
@@ -2770,7 +2782,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>55.22528457641602</v>
+        <v>55.22526931762695</v>
       </c>
       <c r="C99" t="n">
         <v>73.643798828125</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>55.14033508300781</v>
+        <v>55.14032745361328</v>
       </c>
       <c r="C100" t="n">
         <v>73.53052520751953</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>55.84350967407227</v>
+        <v>55.84350204467773</v>
       </c>
       <c r="C101" t="n">
         <v>74.46821594238281</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>55.12162017822266</v>
+        <v>55.12163925170898</v>
       </c>
       <c r="C102" t="n">
         <v>73.14034271240234</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>54.75643157958984</v>
+        <v>54.75641632080078</v>
       </c>
       <c r="C103" t="n">
         <v>72.65576171875</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>49.87128829956055</v>
+        <v>49.87127685546875</v>
       </c>
       <c r="C104" t="n">
         <v>66.17369079589844</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>51.50314712524414</v>
+        <v>51.5031623840332</v>
       </c>
       <c r="C105" t="n">
         <v>67.95468902587891</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>50.36795425415039</v>
+        <v>50.36797332763672</v>
       </c>
       <c r="C106" t="n">
         <v>66.45689392089844</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>51.03572845458984</v>
+        <v>51.03571701049805</v>
       </c>
       <c r="C107" t="n">
         <v>67.33795166015625</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>52.79248809814453</v>
+        <v>52.79249954223633</v>
       </c>
       <c r="C108" t="n">
         <v>69.27627563476562</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>55.15204620361328</v>
+        <v>55.15203475952148</v>
       </c>
       <c r="C109" t="n">
         <v>72.37255859375</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>55.04653167724609</v>
+        <v>55.04653930664062</v>
       </c>
       <c r="C110" t="n">
         <v>72.23410797119141</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>58.7810173034668</v>
+        <v>58.78100204467773</v>
       </c>
       <c r="C111" t="n">
         <v>76.72120666503906</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>56.51003265380859</v>
+        <v>56.5100212097168</v>
       </c>
       <c r="C112" t="n">
         <v>73.757080078125</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>54.84655380249023</v>
+        <v>54.84653854370117</v>
       </c>
       <c r="C113" t="n">
         <v>71.58589935302734</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>56.80533981323242</v>
+        <v>56.80534744262695</v>
       </c>
       <c r="C114" t="n">
         <v>73.73819732666016</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>53.78011322021484</v>
+        <v>53.78011703491211</v>
       </c>
       <c r="C115" t="n">
         <v>69.81120300292969</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>48.63141250610352</v>
+        <v>48.63141632080078</v>
       </c>
       <c r="C116" t="n">
         <v>63.12775421142578</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>44.70369720458984</v>
+        <v>44.70368957519531</v>
       </c>
       <c r="C117" t="n">
         <v>57.65261077880859</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>43.42518997192383</v>
+        <v>43.42519760131836</v>
       </c>
       <c r="C118" t="n">
         <v>56.00377655029297</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>48.02195739746094</v>
+        <v>48.02195358276367</v>
       </c>
       <c r="C119" t="n">
         <v>61.93203353881836</v>
@@ -3408,7 +3420,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>47.18308258056641</v>
+        <v>47.18307113647461</v>
       </c>
       <c r="C121" t="n">
         <v>60.45940780639648</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>43.06740188598633</v>
+        <v>43.06738662719727</v>
       </c>
       <c r="C122" t="n">
         <v>55.18564987182617</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>47.8070068359375</v>
+        <v>47.80699920654297</v>
       </c>
       <c r="C123" t="n">
         <v>60.80553817749023</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>49.52889251708984</v>
+        <v>49.52889633178711</v>
       </c>
       <c r="C124" t="n">
         <v>62.9955940246582</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>51.64166259765625</v>
+        <v>51.64165878295898</v>
       </c>
       <c r="C125" t="n">
         <v>65.68281555175781</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>50.09682464599609</v>
+        <v>50.09682846069336</v>
       </c>
       <c r="C126" t="n">
         <v>63.29767227172852</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>51.07804489135742</v>
+        <v>51.07804107666016</v>
       </c>
       <c r="C127" t="n">
         <v>64.53744506835938</v>
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>53.61826705932617</v>
+        <v>53.61825942993164</v>
       </c>
       <c r="C128" t="n">
         <v>67.74700927734375</v>
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>53.33304977416992</v>
+        <v>53.33306121826172</v>
       </c>
       <c r="C129" t="n">
         <v>66.97923278808594</v>
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>50.91270065307617</v>
+        <v>50.91269683837891</v>
       </c>
       <c r="C130" t="n">
         <v>63.9395866394043</v>
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>51.21336364746094</v>
+        <v>51.2133674621582</v>
       </c>
       <c r="C131" t="n">
         <v>64.31718444824219</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>54.31238174438477</v>
+        <v>54.31237030029297</v>
       </c>
       <c r="C132" t="n">
         <v>67.79106140136719</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>55.27034759521484</v>
+        <v>55.27036285400391</v>
       </c>
       <c r="C133" t="n">
         <v>68.98678588867188</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>55.29557418823242</v>
+        <v>55.29556274414062</v>
       </c>
       <c r="C134" t="n">
         <v>69.01824951171875</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>57.08535385131836</v>
+        <v>57.08534622192383</v>
       </c>
       <c r="C135" t="n">
         <v>70.83071136474609</v>
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>56.91292190551758</v>
+        <v>56.91291046142578</v>
       </c>
       <c r="C136" t="n">
         <v>70.61673736572266</v>
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>60.35173416137695</v>
+        <v>60.35173034667969</v>
       </c>
       <c r="C137" t="n">
         <v>74.88357543945312</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>61.84944534301758</v>
+        <v>61.84945297241211</v>
       </c>
       <c r="C138" t="n">
         <v>76.32472991943359</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>62.27272796630859</v>
+        <v>62.27275085449219</v>
       </c>
       <c r="C139" t="n">
         <v>76.84707641601562</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>60.46743774414062</v>
+        <v>60.46744155883789</v>
       </c>
       <c r="C140" t="n">
         <v>74.61925506591797</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>61.42470169067383</v>
+        <v>61.42468643188477</v>
       </c>
       <c r="C141" t="n">
         <v>75.34297943115234</v>
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>59.55711364746094</v>
+        <v>59.55712890625</v>
       </c>
       <c r="C142" t="n">
         <v>73.05223083496094</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>61.44524002075195</v>
+        <v>61.44519805908203</v>
       </c>
       <c r="C143" t="n">
         <v>75.36815643310547</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>62.68555450439453</v>
+        <v>62.68554306030273</v>
       </c>
       <c r="C144" t="n">
         <v>76.43171691894531</v>
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>65.84431457519531</v>
+        <v>65.84432983398438</v>
       </c>
       <c r="C145" t="n">
         <v>80.28319549560547</v>
@@ -4162,11 +4174,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>71.23287200927734</v>
+        <v>71.23287963867188</v>
       </c>
       <c r="C146" t="n">
         <v>86.85337066650391</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>69.93145751953125</v>
+        <v>69.93144226074219</v>
       </c>
       <c r="C147" t="n">
         <v>84.79547119140625</v>
@@ -4220,7 +4232,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>62.35908126831055</v>
+        <v>62.35906600952148</v>
       </c>
       <c r="C149" t="n">
         <v>75.61359405517578</v>
@@ -4278,11 +4290,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>65.14835357666016</v>
+        <v>65.14833831787109</v>
       </c>
       <c r="C150" t="n">
         <v>78.55255126953125</v>
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>65.25791168212891</v>
+        <v>65.2579345703125</v>
       </c>
       <c r="C151" t="n">
         <v>78.68470764160156</v>
@@ -4336,7 +4348,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4365,7 +4377,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>73.36195373535156</v>
+        <v>73.36196136474609</v>
       </c>
       <c r="C154" t="n">
         <v>87.98615264892578</v>
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>65.17622375488281</v>
+        <v>65.17625427246094</v>
       </c>
       <c r="C155" t="n">
         <v>78.16866302490234</v>
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>64.29930877685547</v>
+        <v>64.29928588867188</v>
       </c>
       <c r="C156" t="n">
         <v>76.67715454101562</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>56.19328308105469</v>
+        <v>56.19329452514648</v>
       </c>
       <c r="C157" t="n">
         <v>67.01069641113281</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>62.30976104736328</v>
+        <v>62.30975341796875</v>
       </c>
       <c r="C158" t="n">
         <v>74.30459594726562</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>66.71465301513672</v>
+        <v>66.71464538574219</v>
       </c>
       <c r="C159" t="n">
         <v>79.08747863769531</v>
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>68.42403411865234</v>
+        <v>68.42405700683594</v>
       </c>
       <c r="C160" t="n">
         <v>81.11390686035156</v>
@@ -4597,11 +4609,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>75.70759582519531</v>
+        <v>75.70760345458984</v>
       </c>
       <c r="C161" t="n">
         <v>89.74826812744141</v>
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>67.41893768310547</v>
+        <v>67.41893005371094</v>
       </c>
       <c r="C162" t="n">
         <v>79.48395538330078</v>
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>69.50077819824219</v>
+        <v>69.50075531005859</v>
       </c>
       <c r="C163" t="n">
         <v>81.93832397460938</v>
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>71.31568145751953</v>
+        <v>71.31568908691406</v>
       </c>
       <c r="C164" t="n">
         <v>84.07803344726562</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>69.93565368652344</v>
+        <v>69.93564605712891</v>
       </c>
       <c r="C165" t="n">
         <v>81.9635009765625</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>73.30787658691406</v>
+        <v>73.307861328125</v>
       </c>
       <c r="C166" t="n">
         <v>85.91567230224609</v>
@@ -4771,11 +4783,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>77.09890747070312</v>
+        <v>77.09891510009766</v>
       </c>
       <c r="C167" t="n">
         <v>90.35871887207031</v>
@@ -4800,11 +4812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>80.05162048339844</v>
+        <v>80.05162811279297</v>
       </c>
       <c r="C168" t="n">
         <v>93.35430908203125</v>
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>80.81793975830078</v>
+        <v>80.81792449951172</v>
       </c>
       <c r="C169" t="n">
         <v>94.24795532226562</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>81.05537414550781</v>
+        <v>81.05536651611328</v>
       </c>
       <c r="C170" t="n">
         <v>94.52485656738281</v>
@@ -4887,7 +4899,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>51.14740753173828</v>
+        <v>51.14741134643555</v>
       </c>
       <c r="C172" t="n">
         <v>59.3643798828125</v>
@@ -4945,11 +4957,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>55.83926773071289</v>
+        <v>55.83925247192383</v>
       </c>
       <c r="C173" t="n">
         <v>64.80999755859375</v>
@@ -4974,11 +4986,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>56.08180999755859</v>
+        <v>56.08180236816406</v>
       </c>
       <c r="C174" t="n">
         <v>64.51999664306641</v>
@@ -5003,11 +5015,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>53.56107711791992</v>
+        <v>53.56108093261719</v>
       </c>
       <c r="C175" t="n">
         <v>61.61999893188477</v>
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>49.26715469360352</v>
+        <v>49.26716613769531</v>
       </c>
       <c r="C176" t="n">
         <v>56.68000030517578</v>
@@ -5059,7 +5071,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5086,11 +5098,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>50.38696670532227</v>
+        <v>50.38695907592773</v>
       </c>
       <c r="C178" t="n">
         <v>57.54000091552734</v>
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>47.56726455688477</v>
+        <v>47.56725311279297</v>
       </c>
       <c r="C179" t="n">
         <v>54.31999969482422</v>
@@ -5140,11 +5152,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>63.26050186157227</v>
+        <v>63.26051712036133</v>
       </c>
       <c r="C180" t="n">
         <v>71.72000122070312</v>
@@ -5167,11 +5179,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>63.07527542114258</v>
+        <v>63.07526779174805</v>
       </c>
       <c r="C181" t="n">
         <v>71.51000213623047</v>
@@ -5194,11 +5206,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>58.85909652709961</v>
+        <v>58.85908889770508</v>
       </c>
       <c r="C182" t="n">
         <v>66.73000335693359</v>
@@ -5221,11 +5233,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>63.88940048217773</v>
+        <v>63.88937759399414</v>
       </c>
       <c r="C183" t="n">
         <v>71.98999786376953</v>
@@ -5248,11 +5260,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>68.57523345947266</v>
+        <v>68.57524871826172</v>
       </c>
       <c r="C184" t="n">
         <v>77.26999664306641</v>
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>73.87348175048828</v>
+        <v>73.87348937988281</v>
       </c>
       <c r="C185" t="n">
         <v>83.23999786376953</v>
@@ -5302,7 +5314,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5329,11 +5341,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>76.16641998291016</v>
+        <v>76.16644287109375</v>
       </c>
       <c r="C187" t="n">
         <v>85.30999755859375</v>
@@ -5356,11 +5368,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>77.63064575195312</v>
+        <v>77.63065338134766</v>
       </c>
       <c r="C188" t="n">
         <v>86.94999694824219</v>
@@ -5385,11 +5397,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>76.12957763671875</v>
+        <v>76.12960052490234</v>
       </c>
       <c r="C189" t="n">
         <v>84.76000213623047</v>
@@ -5414,11 +5426,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>77.20738983154297</v>
+        <v>77.20741271972656</v>
       </c>
       <c r="C190" t="n">
         <v>85.95999908447266</v>
@@ -5443,11 +5455,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>79.81211853027344</v>
+        <v>79.8121337890625</v>
       </c>
       <c r="C191" t="n">
         <v>88.86000061035156</v>
@@ -5472,11 +5484,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>73.10693359375</v>
+        <v>73.10694122314453</v>
       </c>
       <c r="C192" t="n">
         <v>80.91999816894531</v>
@@ -5501,7 +5513,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5530,11 +5542,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>81.48190307617188</v>
+        <v>81.48188781738281</v>
       </c>
       <c r="C194" t="n">
         <v>90.19000244140625</v>
@@ -5559,11 +5571,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>93.29986572265625</v>
+        <v>93.29987335205078</v>
       </c>
       <c r="C195" t="n">
         <v>102.6999969482422</v>
@@ -5588,11 +5600,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>90.00212097167969</v>
+        <v>90.00214385986328</v>
       </c>
       <c r="C196" t="n">
         <v>99.06999969482422</v>
@@ -5617,7 +5629,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5646,11 +5658,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>86.92994689941406</v>
+        <v>86.92993927001953</v>
       </c>
       <c r="C198" t="n">
         <v>95.12000274658203</v>
@@ -5675,7 +5687,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5704,11 +5716,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>85.18440246582031</v>
+        <v>85.18439483642578</v>
       </c>
       <c r="C200" t="n">
         <v>93.20999908447266</v>
@@ -5733,11 +5745,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>82.49998474121094</v>
+        <v>82.49999237060547</v>
       </c>
       <c r="C201" t="n">
         <v>89.75</v>
@@ -5762,11 +5774,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>75.24733734130859</v>
+        <v>75.24736022949219</v>
       </c>
       <c r="C202" t="n">
         <v>81.86000061035156</v>
@@ -5791,11 +5803,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>87.16042327880859</v>
+        <v>87.16043090820312</v>
       </c>
       <c r="C203" t="n">
         <v>94.81999969482422</v>
@@ -5820,11 +5832,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>91.27748107910156</v>
+        <v>91.27748870849609</v>
       </c>
       <c r="C204" t="n">
         <v>98.72000122070312</v>
@@ -5849,11 +5861,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>93.31162261962891</v>
+        <v>93.31163024902344</v>
       </c>
       <c r="C205" t="n">
         <v>100.9199981689453</v>
@@ -5878,11 +5890,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>92.32230377197266</v>
+        <v>92.32227325439453</v>
       </c>
       <c r="C206" t="n">
         <v>99.84999847412109</v>
@@ -5907,11 +5919,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>91.19398498535156</v>
+        <v>91.19397735595703</v>
       </c>
       <c r="C207" t="n">
         <v>98.08999633789062</v>
@@ -5936,11 +5948,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>91.04523468017578</v>
+        <v>91.04524230957031</v>
       </c>
       <c r="C208" t="n">
         <v>97.93000030517578</v>
@@ -5965,11 +5977,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>92.87675476074219</v>
+        <v>92.87673187255859</v>
       </c>
       <c r="C209" t="n">
         <v>99.90000152587891</v>
@@ -5994,11 +6006,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>86.18888092041016</v>
+        <v>86.18887329101562</v>
       </c>
       <c r="C210" t="n">
         <v>92.13999938964844</v>
@@ -6023,11 +6035,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>91.63298034667969</v>
+        <v>91.63297271728516</v>
       </c>
       <c r="C211" t="n">
         <v>97.95999908447266</v>
@@ -6052,11 +6064,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>82.25077819824219</v>
+        <v>82.25078582763672</v>
       </c>
       <c r="C212" t="n">
         <v>87.93000030517578</v>
@@ -6081,11 +6093,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>81.04447174072266</v>
+        <v>81.04447937011719</v>
       </c>
       <c r="C213" t="n">
         <v>86.04000091552734</v>
@@ -6110,11 +6122,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>67.7913818359375</v>
+        <v>67.79137420654297</v>
       </c>
       <c r="C214" t="n">
         <v>71.97000122070312</v>
@@ -6139,11 +6151,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>76.66445922851562</v>
+        <v>76.66446685791016</v>
       </c>
       <c r="C215" t="n">
         <v>81.38999938964844</v>
@@ -6168,11 +6180,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>77.31497955322266</v>
+        <v>77.31498718261719</v>
       </c>
       <c r="C216" t="n">
         <v>81.48000335693359</v>
@@ -6197,7 +6209,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6226,7 +6238,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6255,7 +6267,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6284,7 +6296,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6313,11 +6325,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>96.96476745605469</v>
+        <v>96.96475982666016</v>
       </c>
       <c r="C221" t="n">
         <v>101.5199966430664</v>
@@ -6342,11 +6354,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>103.5920181274414</v>
+        <v>103.5920257568359</v>
       </c>
       <c r="C222" t="n">
         <v>107.8099975585938</v>
@@ -6371,11 +6383,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>96.46231842041016</v>
+        <v>96.46232604980469</v>
       </c>
       <c r="C223" t="n">
         <v>100.3899993896484</v>
@@ -6400,7 +6412,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6429,11 +6441,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>119.1486129760742</v>
+        <v>119.1486206054688</v>
       </c>
       <c r="C225" t="n">
         <v>123.3399963378906</v>
@@ -6458,7 +6470,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6487,7 +6499,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6516,11 +6528,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>118.3167343139648</v>
+        <v>118.3167266845703</v>
       </c>
       <c r="C228" t="n">
         <v>121.8300018310547</v>
@@ -6545,7 +6557,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6574,11 +6586,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>125.2313995361328</v>
+        <v>125.2314147949219</v>
       </c>
       <c r="C230" t="n">
         <v>128.9499969482422</v>
@@ -6603,11 +6615,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>129.8085784912109</v>
+        <v>129.8085632324219</v>
       </c>
       <c r="C231" t="n">
         <v>132.9900054931641</v>
@@ -6632,11 +6644,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>129.291259765625</v>
+        <v>129.2912445068359</v>
       </c>
       <c r="C232" t="n">
         <v>132.4600067138672</v>
@@ -6661,7 +6673,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6690,7 +6702,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6719,11 +6731,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>143.2534332275391</v>
+        <v>143.2534484863281</v>
       </c>
       <c r="C235" t="n">
         <v>146.0200042724609</v>
@@ -6748,7 +6760,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6777,7 +6789,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6806,11 +6818,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>164.8826599121094</v>
+        <v>164.8826904296875</v>
       </c>
       <c r="C238" t="n">
         <v>167.3300018310547</v>
@@ -6835,11 +6847,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>175.8893127441406</v>
+        <v>175.8892974853516</v>
       </c>
       <c r="C239" t="n">
         <v>178.5</v>
@@ -6864,7 +6876,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6893,11 +6905,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>181.431884765625</v>
+        <v>181.4319000244141</v>
       </c>
       <c r="C241" t="n">
         <v>183.3999938964844</v>
@@ -6922,7 +6934,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6951,7 +6963,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6980,7 +6992,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7009,11 +7021,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>174.7590942382812</v>
+        <v>174.7590789794922</v>
       </c>
       <c r="C245" t="n">
         <v>176.0700073242188</v>
@@ -7038,7 +7050,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7067,7 +7079,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7096,7 +7108,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7154,32 +7166,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>192.1900024414062</v>
+        <v>188.6100006103516</v>
       </c>
       <c r="C250" t="n">
-        <v>192.1900024414062</v>
+        <v>188.6100006103516</v>
       </c>
       <c r="D250" t="n">
-        <v>64568900</v>
+        <v>67977600</v>
       </c>
       <c r="E250" t="n">
         <v>5.680000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>33.83626803545884</v>
+        <v>33.20598602294921</v>
       </c>
       <c r="G250" t="n">
         <v>1347758144</v>
       </c>
       <c r="H250" t="n">
-        <v>259025640985.7852</v>
+        <v>254200664362.4463</v>
       </c>
       <c r="I250" t="n">
-        <v>0.04790837309160419</v>
+        <v>0.05043753606878595</v>
       </c>
     </row>
   </sheetData>
@@ -7211,75 +7223,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7315,13 +7327,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7357,13 +7369,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40294</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7399,13 +7411,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7483,13 +7495,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7516,7 +7528,7 @@
       <c r="I7" t="n">
         <v>2.592825676526117</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K7" t="n">
@@ -7529,13 +7541,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40294</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7562,7 +7574,7 @@
       <c r="I8" t="n">
         <v>2.687224669603524</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K8" t="n">
@@ -7575,13 +7587,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40385</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7608,7 +7620,7 @@
       <c r="I9" t="n">
         <v>2.781623662680931</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K9" t="n">
@@ -7621,13 +7633,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40476</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7654,7 +7666,7 @@
       <c r="I10" t="n">
         <v>2.882315921963499</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K10" t="n">
@@ -7667,13 +7679,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7700,7 +7712,7 @@
       <c r="I11" t="n">
         <v>2.983008181246067</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K11" t="n">
@@ -7713,13 +7725,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40658</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7746,7 +7758,7 @@
       <c r="I12" t="n">
         <v>3.096286972938955</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40658</v>
       </c>
       <c r="K12" t="n">
@@ -7759,13 +7771,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40749</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7792,7 +7804,7 @@
       <c r="I13" t="n">
         <v>3.253618628067967</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40749</v>
       </c>
       <c r="K13" t="n">
@@ -7805,13 +7817,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40840</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7838,7 +7850,7 @@
       <c r="I14" t="n">
         <v>3.360604153555696</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40840</v>
       </c>
       <c r="K14" t="n">
@@ -7851,13 +7863,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7884,7 +7896,7 @@
       <c r="I15" t="n">
         <v>3.461296412838263</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="K15" t="n">
@@ -7897,13 +7909,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7930,7 +7942,7 @@
       <c r="I16" t="n">
         <v>2.989301447451227</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="K16" t="n">
@@ -7943,13 +7955,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41120</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7976,7 +7988,7 @@
       <c r="I17" t="n">
         <v>3.001887979861548</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41120</v>
       </c>
       <c r="K17" t="n">
@@ -7989,13 +8001,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8022,7 +8034,7 @@
       <c r="I18" t="n">
         <v>3.058527375707992</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="K18" t="n">
@@ -8035,13 +8047,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41312</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8068,7 +8080,7 @@
       <c r="I19" t="n">
         <v>3.55569540591567</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41312</v>
       </c>
       <c r="K19" t="n">
@@ -8081,13 +8093,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8114,7 +8126,7 @@
       <c r="I20" t="n">
         <v>4.2039018250472</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="K20" t="n">
@@ -8127,13 +8139,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8160,7 +8172,7 @@
       <c r="I21" t="n">
         <v>4.354940213971051</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="K21" t="n">
@@ -8173,13 +8185,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8206,7 +8218,7 @@
       <c r="I22" t="n">
         <v>4.361233480176211</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="K22" t="n">
@@ -8219,13 +8231,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8252,7 +8264,7 @@
       <c r="I23" t="n">
         <v>3.94587791063562</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="K23" t="n">
@@ -8265,13 +8277,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8298,7 +8310,7 @@
       <c r="I24" t="n">
         <v>3.901825047199496</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="K24" t="n">
@@ -8311,13 +8323,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8344,7 +8356,7 @@
       <c r="I25" t="n">
         <v>3.983637507866582</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="K25" t="n">
@@ -8357,13 +8369,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8390,7 +8402,7 @@
       <c r="I26" t="n">
         <v>4.279421019509125</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="K26" t="n">
@@ -8403,13 +8415,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42040</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8436,7 +8448,7 @@
       <c r="I27" t="n">
         <v>4.292007551919447</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42040</v>
       </c>
       <c r="K27" t="n">
@@ -8449,13 +8461,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8482,7 +8494,7 @@
       <c r="I28" t="n">
         <v>4.455632473253619</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="K28" t="n">
@@ -8495,13 +8507,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8528,7 +8540,7 @@
       <c r="I29" t="n">
         <v>4.386406544996854</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="K29" t="n">
@@ -8541,13 +8553,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8574,7 +8586,7 @@
       <c r="I30" t="n">
         <v>4.07174323473883</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="K30" t="n">
@@ -8587,13 +8599,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8620,7 +8632,7 @@
       <c r="I31" t="n">
         <v>5.481434864694776</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K31" t="n">
@@ -8633,13 +8645,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8666,7 +8678,7 @@
       <c r="I32" t="n">
         <v>5.387035871617369</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K32" t="n">
@@ -8679,13 +8691,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8712,7 +8724,7 @@
       <c r="I33" t="n">
         <v>5.336689741976086</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="K33" t="n">
@@ -8725,13 +8737,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8758,7 +8770,7 @@
       <c r="I34" t="n">
         <v>5.487728130899937</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="K34" t="n">
@@ -8771,13 +8783,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8804,7 +8816,7 @@
       <c r="I35" t="n">
         <v>3.845185651353052</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="K35" t="n">
@@ -8817,13 +8829,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8850,7 +8862,7 @@
       <c r="I36" t="n">
         <v>4.033983637507866</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="K36" t="n">
@@ -8863,13 +8875,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8896,7 +8908,7 @@
       <c r="I37" t="n">
         <v>4.128382630585274</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K37" t="n">
@@ -8909,13 +8921,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8942,7 +8954,7 @@
       <c r="I38" t="n">
         <v>4.059156702328509</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K38" t="n">
@@ -8955,13 +8967,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8988,7 +9000,7 @@
       <c r="I39" t="n">
         <v>3.587161736941473</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="K39" t="n">
@@ -9001,13 +9013,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9034,7 +9046,7 @@
       <c r="I40" t="n">
         <v>3.517935808684707</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K40" t="n">
@@ -9047,13 +9059,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9080,7 +9092,7 @@
       <c r="I41" t="n">
         <v>3.996224040276904</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K41" t="n">
@@ -9093,13 +9105,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9126,7 +9138,7 @@
       <c r="I42" t="n">
         <v>3.914411579609818</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K42" t="n">
@@ -9139,13 +9151,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9172,7 +9184,7 @@
       <c r="I43" t="n">
         <v>4.122089364380114</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="K43" t="n">
@@ -9185,13 +9197,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9218,7 +9230,7 @@
       <c r="I44" t="n">
         <v>4.084329767149151</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K44" t="n">
@@ -9231,13 +9243,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9264,7 +9276,7 @@
       <c r="I45" t="n">
         <v>3.857772183763374</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K45" t="n">
@@ -9277,13 +9289,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9310,7 +9322,7 @@
       <c r="I46" t="n">
         <v>3.725613593455003</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="K46" t="n">
@@ -9323,13 +9335,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9356,7 +9368,7 @@
       <c r="I47" t="n">
         <v>4.033983637507867</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="K47" t="n">
@@ -9369,13 +9381,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9402,7 +9414,7 @@
       <c r="I48" t="n">
         <v>2.952234109502832</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K48" t="n">
@@ -9415,13 +9427,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9448,7 +9460,7 @@
       <c r="I49" t="n">
         <v>-0.982284455632473</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K49" t="n">
@@ -9461,13 +9473,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9494,7 +9506,7 @@
       <c r="I50" t="n">
         <v>-1.649288860918817</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="K50" t="n">
@@ -9507,13 +9519,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44235</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9540,7 +9552,7 @@
       <c r="I51" t="n">
         <v>-2.39</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44235</v>
       </c>
       <c r="K51" t="n">
@@ -9553,13 +9565,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9586,7 +9598,7 @@
       <c r="I52" t="n">
         <v>-1.79</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="K52" t="n">
@@ -9599,13 +9611,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9632,7 +9644,7 @@
       <c r="I53" t="n">
         <v>1.44</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="K53" t="n">
@@ -9645,13 +9657,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9678,7 +9690,7 @@
       <c r="I54" t="n">
         <v>2.2</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="K54" t="n">
@@ -9691,13 +9703,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9724,7 +9736,7 @@
       <c r="I55" t="n">
         <v>2.56</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="K55" t="n">
@@ -9737,13 +9749,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9770,7 +9782,7 @@
       <c r="I56" t="n">
         <v>2.779999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="K56" t="n">
@@ -9783,13 +9795,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9816,7 +9828,7 @@
       <c r="I57" t="n">
         <v>2.98</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="K57" t="n">
@@ -9829,13 +9841,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9862,7 +9874,7 @@
       <c r="I58" t="n">
         <v>2.99</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="K58" t="n">
@@ -9875,13 +9887,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9908,7 +9920,7 @@
       <c r="I59" t="n">
         <v>3.5</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="K59" t="n">
@@ -9921,13 +9933,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9954,7 +9966,7 @@
       <c r="I60" t="n">
         <v>3.75</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="K60" t="n">
@@ -9967,13 +9979,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10000,7 +10012,7 @@
       <c r="I61" t="n">
         <v>3.77</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="K61" t="n">
@@ -10013,13 +10025,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10046,7 +10058,7 @@
       <c r="I62" t="n">
         <v>2.15</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="K62" t="n">
@@ -10059,13 +10071,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10092,7 +10104,7 @@
       <c r="I63" t="n">
         <v>2.23</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="K63" t="n">
@@ -10105,13 +10117,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10138,7 +10150,7 @@
       <c r="I64" t="n">
         <v>2.54</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="K64" t="n">
@@ -10151,13 +10163,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10184,7 +10196,7 @@
       <c r="I65" t="n">
         <v>1.72</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K65" t="n">
@@ -10197,13 +10209,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10230,7 +10242,7 @@
       <c r="I66" t="n">
         <v>3.49</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="K66" t="n">
@@ -10243,13 +10255,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10276,7 +10288,7 @@
       <c r="I67" t="n">
         <v>3.55</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="K67" t="n">
@@ -10289,13 +10301,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10322,7 +10334,7 @@
       <c r="I68" t="n">
         <v>3.41</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="K68" t="n">
@@ -10335,13 +10347,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10368,7 +10380,7 @@
       <c r="I69" t="n">
         <v>4.55</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="K69" t="n">
@@ -10381,13 +10393,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10414,7 +10426,7 @@
       <c r="I70" t="n">
         <v>4.869999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="K70" t="n">
@@ -10427,13 +10439,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10460,7 +10472,7 @@
       <c r="I71" t="n">
         <v>4.960000000000001</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="K71" t="n">
@@ -10473,13 +10485,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10506,7 +10518,7 @@
       <c r="I72" t="n">
         <v>5.330000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="K72" t="n">
@@ -10519,13 +10531,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10552,7 +10564,7 @@
       <c r="I73" t="n">
         <v>5.680000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="K73" t="n">
@@ -10589,52 +10601,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="C2" t="n">
@@ -10663,10 +10675,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="C3" t="n">
@@ -10695,10 +10707,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40220</v>
       </c>
       <c r="C4" t="n">
@@ -10727,10 +10739,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40294</v>
       </c>
       <c r="C5" t="n">
@@ -10759,10 +10771,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40385</v>
       </c>
       <c r="C6" t="n">
@@ -10791,10 +10803,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40476</v>
       </c>
       <c r="C7" t="n">
@@ -10823,10 +10835,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="C8" t="n">
@@ -10855,10 +10867,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40658</v>
       </c>
       <c r="C9" t="n">
@@ -10887,10 +10899,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40749</v>
       </c>
       <c r="C10" t="n">
@@ -10919,10 +10931,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40840</v>
       </c>
       <c r="C11" t="n">
@@ -10951,10 +10963,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="C12" t="n">
@@ -10983,10 +10995,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="C13" t="n">
@@ -11015,10 +11027,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41120</v>
       </c>
       <c r="C14" t="n">
@@ -11047,10 +11059,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="C15" t="n">
@@ -11079,10 +11091,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41312</v>
       </c>
       <c r="C16" t="n">
@@ -11111,10 +11123,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="C17" t="n">
@@ -11143,10 +11155,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="C18" t="n">
@@ -11175,10 +11187,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="C19" t="n">
@@ -11207,10 +11219,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="C20" t="n">
@@ -11239,10 +11251,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="C21" t="n">
@@ -11271,10 +11283,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="C22" t="n">
@@ -11303,10 +11315,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="C23" t="n">
@@ -11335,10 +11347,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42040</v>
       </c>
       <c r="C24" t="n">
@@ -11367,10 +11379,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="C25" t="n">
@@ -11399,10 +11411,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="C26" t="n">
@@ -11431,10 +11443,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="C27" t="n">
@@ -11463,10 +11475,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C28" t="n">
@@ -11495,10 +11507,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C29" t="n">
@@ -11527,10 +11539,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="C30" t="n">
@@ -11559,10 +11571,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="C31" t="n">
@@ -11591,10 +11603,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="C32" t="n">
@@ -11623,10 +11635,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="C33" t="n">
@@ -11655,10 +11667,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C34" t="n">
@@ -11687,10 +11699,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C35" t="n">
@@ -11719,10 +11731,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="C36" t="n">
@@ -11751,10 +11763,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C37" t="n">
@@ -11783,10 +11795,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C38" t="n">
@@ -11815,10 +11827,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C39" t="n">
@@ -11847,10 +11859,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="C40" t="n">
@@ -11879,10 +11891,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C41" t="n">
@@ -11911,10 +11923,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C42" t="n">
@@ -11943,10 +11955,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C43" t="n">
@@ -11975,10 +11987,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="C44" t="n">
@@ -12007,10 +12019,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C45" t="n">
@@ -12039,10 +12051,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44033</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C46" t="n">
@@ -12071,10 +12083,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44124</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="C47" t="n">
@@ -12103,10 +12115,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44235</v>
       </c>
       <c r="C48" t="n">
@@ -12135,10 +12147,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="C49" t="n">
@@ -12167,10 +12179,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="C50" t="n">
@@ -12199,10 +12211,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="C51" t="n">
@@ -12231,10 +12243,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="C52" t="n">
@@ -12263,10 +12275,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="C53" t="n">
@@ -12295,10 +12307,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="C54" t="n">
@@ -12327,10 +12339,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="C55" t="n">
@@ -12359,10 +12371,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="C56" t="n">
@@ -12391,10 +12403,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="C57" t="n">
@@ -12423,10 +12435,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="C58" t="n">
@@ -12455,10 +12467,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="C59" t="n">
@@ -12487,10 +12499,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="C60" t="n">
@@ -12519,10 +12531,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="C61" t="n">
@@ -12551,10 +12563,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C62" t="n">
@@ -12583,10 +12595,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="C63" t="n">
@@ -12615,10 +12627,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="C64" t="n">
@@ -12647,10 +12659,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="C65" t="n">
@@ -12679,10 +12691,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="C66" t="n">
@@ -12711,10 +12723,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="C67" t="n">
@@ -12743,10 +12755,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="C68" t="n">
@@ -12775,10 +12787,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C69" t="n">
@@ -12807,10 +12819,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="C70" t="n">
@@ -12857,12 +12869,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/RTX.xlsx
+++ b/salidas/empresas/RTX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>22.95646858215332</v>
+        <v>22.95646476745605</v>
       </c>
       <c r="C2" t="n">
         <v>36.73379516601562</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>23.09499931335449</v>
+        <v>23.09499549865723</v>
       </c>
       <c r="C3" t="n">
         <v>36.81560516357422</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>24.79653358459473</v>
+        <v>24.79652404785156</v>
       </c>
       <c r="C5" t="n">
         <v>39.52800369262695</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>24.78279113769531</v>
+        <v>24.78279495239258</v>
       </c>
       <c r="C6" t="n">
         <v>39.34550094604492</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>25.1395435333252</v>
+        <v>25.13953399658203</v>
       </c>
       <c r="C7" t="n">
         <v>39.91189575195312</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>24.6519775390625</v>
+        <v>24.6519660949707</v>
       </c>
       <c r="C8" t="n">
         <v>39.13782119750977</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>24.96650123596191</v>
+        <v>24.96650886535645</v>
       </c>
       <c r="C9" t="n">
         <v>39.46507263183594</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>25.2213020324707</v>
+        <v>25.2213077545166</v>
       </c>
       <c r="C10" t="n">
         <v>39.86783981323242</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>26.16486358642578</v>
+        <v>26.16487693786621</v>
       </c>
       <c r="C11" t="n">
         <v>41.35934448242188</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>25.79528427124023</v>
+        <v>25.7952766418457</v>
       </c>
       <c r="C12" t="n">
         <v>40.61044692993164</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>24.99180793762207</v>
+        <v>24.9918155670166</v>
       </c>
       <c r="C13" t="n">
         <v>39.34550094604492</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>27.19038200378418</v>
+        <v>27.19038391113281</v>
       </c>
       <c r="C14" t="n">
         <v>42.80679702758789</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>26.34288597106934</v>
+        <v>26.34288215637207</v>
       </c>
       <c r="C15" t="n">
         <v>41.30899810791016</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>26.08603286743164</v>
+        <v>26.08602905273438</v>
       </c>
       <c r="C16" t="n">
         <v>40.90623092651367</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>28.42333793640137</v>
+        <v>28.4233341217041</v>
       </c>
       <c r="C18" t="n">
         <v>44.39899444580078</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>28.57643890380859</v>
+        <v>28.57644081115723</v>
       </c>
       <c r="C19" t="n">
         <v>44.63813781738281</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>29.39831352233887</v>
+        <v>29.39830780029297</v>
       </c>
       <c r="C20" t="n">
         <v>45.92196273803711</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>30.19987678527832</v>
+        <v>30.19986724853516</v>
       </c>
       <c r="C21" t="n">
         <v>46.96664428710938</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>32.56715393066406</v>
+        <v>32.56714630126953</v>
       </c>
       <c r="C22" t="n">
         <v>50.6482048034668</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>30.99300956726074</v>
+        <v>30.99302101135254</v>
       </c>
       <c r="C23" t="n">
         <v>48.20012664794922</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>30.3856086730957</v>
+        <v>30.38561630249023</v>
       </c>
       <c r="C24" t="n">
         <v>47.05475234985352</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>31.10490798950195</v>
+        <v>31.10491371154785</v>
       </c>
       <c r="C25" t="n">
         <v>48.16865921020508</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>29.77602005004883</v>
+        <v>29.77602958679199</v>
       </c>
       <c r="C26" t="n">
         <v>46.11075973510742</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>28.7808780670166</v>
+        <v>28.7808723449707</v>
       </c>
       <c r="C27" t="n">
         <v>44.37382125854492</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>28.09103584289551</v>
+        <v>28.09104156494141</v>
       </c>
       <c r="C28" t="n">
         <v>43.31025695800781</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>29.58090972900391</v>
+        <v>29.58090400695801</v>
       </c>
       <c r="C29" t="n">
         <v>45.6072998046875</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>29.1215934753418</v>
+        <v>29.12160491943359</v>
       </c>
       <c r="C30" t="n">
         <v>44.70736312866211</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>25.29281997680664</v>
+        <v>25.29282188415527</v>
       </c>
       <c r="C31" t="n">
         <v>38.82945251464844</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>26.22747230529785</v>
+        <v>26.22747421264648</v>
       </c>
       <c r="C32" t="n">
         <v>40.26431655883789</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>27.0174446105957</v>
+        <v>27.01745986938477</v>
       </c>
       <c r="C33" t="n">
         <v>41.27753448486328</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.73955917358398</v>
+        <v>24.73957252502441</v>
       </c>
       <c r="C34" t="n">
         <v>37.79735565185547</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>22.6388111114502</v>
+        <v>22.63880348205566</v>
       </c>
       <c r="C35" t="n">
         <v>34.58779144287109</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.1398868560791</v>
+        <v>20.1398811340332</v>
       </c>
       <c r="C36" t="n">
         <v>30.54122161865234</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>22.24393272399902</v>
+        <v>22.24393081665039</v>
       </c>
       <c r="C37" t="n">
         <v>33.73190689086914</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>19.91578674316406</v>
+        <v>19.91578483581543</v>
       </c>
       <c r="C38" t="n">
         <v>30.20138549804688</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>17.08842277526855</v>
+        <v>17.08842086791992</v>
       </c>
       <c r="C39" t="n">
         <v>25.69540596008301</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>17.98826026916504</v>
+        <v>17.98825073242188</v>
       </c>
       <c r="C40" t="n">
         <v>27.04845809936523</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.44080352783203</v>
+        <v>20.4408130645752</v>
       </c>
       <c r="C41" t="n">
         <v>30.73631286621094</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>22.18027496337891</v>
+        <v>22.18026351928711</v>
       </c>
       <c r="C42" t="n">
         <v>33.1088752746582</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.96443939208984</v>
+        <v>22.96444320678711</v>
       </c>
       <c r="C44" t="n">
         <v>34.27942276000977</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>25.19681358337402</v>
+        <v>25.19681549072266</v>
       </c>
       <c r="C45" t="n">
         <v>37.35682678222656</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>25.86323356628418</v>
+        <v>25.86323547363281</v>
       </c>
       <c r="C46" t="n">
         <v>38.34487152099609</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>26.08396530151367</v>
+        <v>26.08396339416504</v>
       </c>
       <c r="C47" t="n">
         <v>38.672119140625</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>28.69967842102051</v>
+        <v>28.69968032836914</v>
       </c>
       <c r="C48" t="n">
         <v>42.31592178344727</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>29.62587928771973</v>
+        <v>29.62587738037109</v>
       </c>
       <c r="C49" t="n">
         <v>43.68156051635742</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>28.80211639404297</v>
+        <v>28.8021125793457</v>
       </c>
       <c r="C50" t="n">
         <v>42.46696090698242</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>29.49045372009277</v>
+        <v>29.49045753479004</v>
       </c>
       <c r="C51" t="n">
         <v>43.20327377319336</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>32.19678115844727</v>
+        <v>32.19679641723633</v>
       </c>
       <c r="C53" t="n">
         <v>47.16802978515625</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>29.11408805847168</v>
+        <v>29.11409950256348</v>
       </c>
       <c r="C54" t="n">
         <v>42.40402984619141</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>28.34732627868652</v>
+        <v>28.34733390808105</v>
       </c>
       <c r="C57" t="n">
         <v>41.03838729858398</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>30.96427917480469</v>
+        <v>30.96425247192383</v>
       </c>
       <c r="C58" t="n">
         <v>44.82693481445312</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>32.90908813476562</v>
+        <v>32.90908432006836</v>
       </c>
       <c r="C60" t="n">
         <v>47.36941528320312</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>34.41748809814453</v>
+        <v>34.41747665405273</v>
       </c>
       <c r="C61" t="n">
         <v>49.54059219360352</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>35.54549789428711</v>
+        <v>35.54548263549805</v>
       </c>
       <c r="C62" t="n">
         <v>51.16425323486328</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>36.70853805541992</v>
+        <v>36.70853042602539</v>
       </c>
       <c r="C63" t="n">
         <v>52.57394790649414</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>37.19628143310547</v>
+        <v>37.19629287719727</v>
       </c>
       <c r="C64" t="n">
         <v>53.27249908447266</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>39.36258316040039</v>
+        <v>39.36259460449219</v>
       </c>
       <c r="C65" t="n">
         <v>56.37508010864258</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>38.77920150756836</v>
+        <v>38.77921676635742</v>
       </c>
       <c r="C66" t="n">
         <v>55.23599624633789</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>39.10616683959961</v>
+        <v>39.10616302490234</v>
       </c>
       <c r="C67" t="n">
         <v>55.70169830322266</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>36.60101318359375</v>
+        <v>36.60100173950195</v>
       </c>
       <c r="C68" t="n">
         <v>52.13341522216797</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>33.02419662475586</v>
+        <v>33.02419281005859</v>
       </c>
       <c r="C69" t="n">
         <v>46.72750091552734</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>31.29403877258301</v>
+        <v>31.29404067993164</v>
       </c>
       <c r="C70" t="n">
         <v>44.27942276000977</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>34.68318557739258</v>
+        <v>34.68317794799805</v>
       </c>
       <c r="C71" t="n">
         <v>49.07489013671875</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>32.70614242553711</v>
+        <v>32.70615005493164</v>
       </c>
       <c r="C73" t="n">
         <v>45.99748229980469</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>35.05989456176758</v>
+        <v>35.05988311767578</v>
       </c>
       <c r="C74" t="n">
         <v>49.3077392578125</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>37.32548522949219</v>
+        <v>37.32548904418945</v>
       </c>
       <c r="C76" t="n">
         <v>52.19635009765625</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>36.74044036865234</v>
+        <v>36.74044799804688</v>
       </c>
       <c r="C77" t="n">
         <v>51.37822341918945</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>33.56322860717773</v>
+        <v>33.5632209777832</v>
       </c>
       <c r="C78" t="n">
         <v>46.63939666748047</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>34.20631790161133</v>
+        <v>34.20632934570312</v>
       </c>
       <c r="C79" t="n">
         <v>47.53303909301758</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>36.41325759887695</v>
+        <v>36.41324615478516</v>
       </c>
       <c r="C81" t="n">
         <v>50.25173187255859</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>35.70185470581055</v>
+        <v>35.70185852050781</v>
       </c>
       <c r="C82" t="n">
         <v>49.26998138427734</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>35.64257049560547</v>
+        <v>35.6425666809082</v>
       </c>
       <c r="C83" t="n">
         <v>49.18816757202148</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>36.78741836547852</v>
+        <v>36.78741455078125</v>
       </c>
       <c r="C84" t="n">
         <v>50.41535568237305</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>37.65991973876953</v>
+        <v>37.65990447998047</v>
       </c>
       <c r="C85" t="n">
         <v>51.61107635498047</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>40.21313095092773</v>
+        <v>40.21312713623047</v>
       </c>
       <c r="C86" t="n">
         <v>55.11013031005859</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>43.16072463989258</v>
+        <v>43.16073989868164</v>
       </c>
       <c r="C88" t="n">
         <v>58.7979850769043</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>44.08567047119141</v>
+        <v>44.08567810058594</v>
       </c>
       <c r="C90" t="n">
         <v>59.72309494018555</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>43.17516708374023</v>
+        <v>43.17516326904297</v>
       </c>
       <c r="C91" t="n">
         <v>58.48961639404297</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>49.04241180419922</v>
+        <v>49.04240417480469</v>
       </c>
       <c r="C92" t="n">
         <v>66.43801116943359</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>46.73543167114258</v>
+        <v>46.73544311523438</v>
       </c>
       <c r="C93" t="n">
         <v>62.9955940246582</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>49.60678482055664</v>
+        <v>49.60680770874023</v>
       </c>
       <c r="C95" t="n">
         <v>66.86595153808594</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>52.04493713378906</v>
+        <v>52.04490661621094</v>
       </c>
       <c r="C96" t="n">
         <v>69.76715087890625</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>53.4251594543457</v>
+        <v>53.42515182495117</v>
       </c>
       <c r="C97" t="n">
         <v>71.61737060546875</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>53.52842712402344</v>
+        <v>53.52842330932617</v>
       </c>
       <c r="C98" t="n">
         <v>71.75582122802734</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>55.22526931762695</v>
+        <v>55.22527694702148</v>
       </c>
       <c r="C99" t="n">
         <v>73.643798828125</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>55.14032745361328</v>
+        <v>55.14031982421875</v>
       </c>
       <c r="C100" t="n">
         <v>73.53052520751953</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>55.12163925170898</v>
+        <v>55.12162017822266</v>
       </c>
       <c r="C102" t="n">
         <v>73.14034271240234</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>54.75641632080078</v>
+        <v>54.75641250610352</v>
       </c>
       <c r="C103" t="n">
         <v>72.65576171875</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>51.5031623840332</v>
+        <v>51.50313949584961</v>
       </c>
       <c r="C105" t="n">
         <v>67.95468902587891</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>50.36797332763672</v>
+        <v>50.36796188354492</v>
       </c>
       <c r="C106" t="n">
         <v>66.45689392089844</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>51.03571701049805</v>
+        <v>51.03573226928711</v>
       </c>
       <c r="C107" t="n">
         <v>67.33795166015625</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>52.79249954223633</v>
+        <v>52.79250335693359</v>
       </c>
       <c r="C108" t="n">
         <v>69.27627563476562</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>55.15203475952148</v>
+        <v>55.15204238891602</v>
       </c>
       <c r="C109" t="n">
         <v>72.37255859375</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>55.04653930664062</v>
+        <v>55.04652786254883</v>
       </c>
       <c r="C110" t="n">
         <v>72.23410797119141</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>58.78100204467773</v>
+        <v>58.78104019165039</v>
       </c>
       <c r="C111" t="n">
         <v>76.72120666503906</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>56.5100212097168</v>
+        <v>56.51003646850586</v>
       </c>
       <c r="C112" t="n">
         <v>73.757080078125</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>54.84653854370117</v>
+        <v>54.84653472900391</v>
       </c>
       <c r="C113" t="n">
         <v>71.58589935302734</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>56.80534744262695</v>
+        <v>56.80533981323242</v>
       </c>
       <c r="C114" t="n">
         <v>73.73819732666016</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>53.78011703491211</v>
+        <v>53.78010940551758</v>
       </c>
       <c r="C115" t="n">
         <v>69.81120300292969</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>48.63141632080078</v>
+        <v>48.63141250610352</v>
       </c>
       <c r="C116" t="n">
         <v>63.12775421142578</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>44.70368957519531</v>
+        <v>44.70369338989258</v>
       </c>
       <c r="C117" t="n">
         <v>57.65261077880859</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>48.02195358276367</v>
+        <v>48.02196502685547</v>
       </c>
       <c r="C119" t="n">
         <v>61.93203353881836</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>47.17325973510742</v>
+        <v>47.17327117919922</v>
       </c>
       <c r="C120" t="n">
         <v>60.44682312011719</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>47.18307113647461</v>
+        <v>47.18307876586914</v>
       </c>
       <c r="C121" t="n">
         <v>60.45940780639648</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>43.06738662719727</v>
+        <v>43.06739044189453</v>
       </c>
       <c r="C122" t="n">
         <v>55.18564987182617</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>47.80699920654297</v>
+        <v>47.80700302124023</v>
       </c>
       <c r="C123" t="n">
         <v>60.80553817749023</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>49.52889633178711</v>
+        <v>49.52887725830078</v>
       </c>
       <c r="C124" t="n">
         <v>62.9955940246582</v>
@@ -3569,7 +3569,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>51.64165878295898</v>
+        <v>51.64165115356445</v>
       </c>
       <c r="C125" t="n">
         <v>65.68281555175781</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>50.09682846069336</v>
+        <v>50.09683609008789</v>
       </c>
       <c r="C126" t="n">
         <v>63.29767227172852</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>51.07804107666016</v>
+        <v>51.07805252075195</v>
       </c>
       <c r="C127" t="n">
         <v>64.53744506835938</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>53.61825942993164</v>
+        <v>53.61826705932617</v>
       </c>
       <c r="C128" t="n">
         <v>67.74700927734375</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>53.33306121826172</v>
+        <v>53.33304595947266</v>
       </c>
       <c r="C129" t="n">
         <v>66.97923278808594</v>
@@ -3714,7 +3714,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>50.91269683837891</v>
+        <v>50.91269302368164</v>
       </c>
       <c r="C130" t="n">
         <v>63.9395866394043</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>55.29556274414062</v>
+        <v>55.29555511474609</v>
       </c>
       <c r="C134" t="n">
         <v>69.01824951171875</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>57.08534622192383</v>
+        <v>57.08536148071289</v>
       </c>
       <c r="C135" t="n">
         <v>70.83071136474609</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>56.91291046142578</v>
+        <v>56.91291427612305</v>
       </c>
       <c r="C136" t="n">
         <v>70.61673736572266</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>60.35173034667969</v>
+        <v>60.35171127319336</v>
       </c>
       <c r="C137" t="n">
         <v>74.88357543945312</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>61.84945297241211</v>
+        <v>61.84946441650391</v>
       </c>
       <c r="C138" t="n">
         <v>76.32472991943359</v>
@@ -3975,7 +3975,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>62.27275085449219</v>
+        <v>62.27274322509766</v>
       </c>
       <c r="C139" t="n">
         <v>76.84707641601562</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>60.46744155883789</v>
+        <v>60.46743392944336</v>
       </c>
       <c r="C140" t="n">
         <v>74.61925506591797</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>61.42468643188477</v>
+        <v>61.4246940612793</v>
       </c>
       <c r="C141" t="n">
         <v>75.34297943115234</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>59.55712890625</v>
+        <v>59.55710983276367</v>
       </c>
       <c r="C142" t="n">
         <v>73.05223083496094</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>61.44519805908203</v>
+        <v>61.44523239135742</v>
       </c>
       <c r="C143" t="n">
         <v>75.36815643310547</v>
@@ -4120,7 +4120,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>62.68554306030273</v>
+        <v>62.68552017211914</v>
       </c>
       <c r="C144" t="n">
         <v>76.43171691894531</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>65.84432983398438</v>
+        <v>65.84434509277344</v>
       </c>
       <c r="C145" t="n">
         <v>80.28319549560547</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>71.23287963867188</v>
+        <v>71.23286437988281</v>
       </c>
       <c r="C146" t="n">
         <v>86.85337066650391</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>69.93144226074219</v>
+        <v>69.93144989013672</v>
       </c>
       <c r="C147" t="n">
         <v>84.79547119140625</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>65.30185699462891</v>
+        <v>65.30184936523438</v>
       </c>
       <c r="C148" t="n">
         <v>79.18187713623047</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>62.35906600952148</v>
+        <v>62.35908126831055</v>
       </c>
       <c r="C149" t="n">
         <v>75.61359405517578</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>65.14833831787109</v>
+        <v>65.14833068847656</v>
       </c>
       <c r="C150" t="n">
         <v>78.55255126953125</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>65.2579345703125</v>
+        <v>65.25795745849609</v>
       </c>
       <c r="C151" t="n">
         <v>78.68470764160156</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>69.10643005371094</v>
+        <v>69.1064453125</v>
       </c>
       <c r="C153" t="n">
         <v>82.88231658935547</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>65.17625427246094</v>
+        <v>65.17623901367188</v>
       </c>
       <c r="C155" t="n">
         <v>78.16866302490234</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>64.29928588867188</v>
+        <v>64.29930114746094</v>
       </c>
       <c r="C156" t="n">
         <v>76.67715454101562</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>56.19329452514648</v>
+        <v>56.19327163696289</v>
       </c>
       <c r="C157" t="n">
         <v>67.01069641113281</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>62.30975341796875</v>
+        <v>62.30973434448242</v>
       </c>
       <c r="C158" t="n">
         <v>74.30459594726562</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>66.71464538574219</v>
+        <v>66.71463012695312</v>
       </c>
       <c r="C159" t="n">
         <v>79.08747863769531</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>68.42405700683594</v>
+        <v>68.42404937744141</v>
       </c>
       <c r="C160" t="n">
         <v>81.11390686035156</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>67.41893005371094</v>
+        <v>67.4189453125</v>
       </c>
       <c r="C162" t="n">
         <v>79.48395538330078</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>69.93564605712891</v>
+        <v>69.93567657470703</v>
       </c>
       <c r="C165" t="n">
         <v>81.9635009765625</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>73.307861328125</v>
+        <v>73.30786895751953</v>
       </c>
       <c r="C166" t="n">
         <v>85.91567230224609</v>
@@ -4787,7 +4787,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>77.09891510009766</v>
+        <v>77.09889984130859</v>
       </c>
       <c r="C167" t="n">
         <v>90.35871887207031</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>80.05162811279297</v>
+        <v>80.0516357421875</v>
       </c>
       <c r="C168" t="n">
         <v>93.35430908203125</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>81.05536651611328</v>
+        <v>81.05540466308594</v>
       </c>
       <c r="C170" t="n">
         <v>94.52485656738281</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>70.80821228027344</v>
+        <v>70.80823516845703</v>
       </c>
       <c r="C171" t="n">
         <v>82.18376159667969</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>51.14741134643555</v>
+        <v>51.14740753173828</v>
       </c>
       <c r="C172" t="n">
         <v>59.3643798828125</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>55.83925247192383</v>
+        <v>55.83926010131836</v>
       </c>
       <c r="C173" t="n">
         <v>64.80999755859375</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>56.08180236816406</v>
+        <v>56.0817985534668</v>
       </c>
       <c r="C174" t="n">
         <v>64.51999664306641</v>
@@ -5019,7 +5019,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>53.56108093261719</v>
+        <v>53.56107330322266</v>
       </c>
       <c r="C175" t="n">
         <v>61.61999893188477</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>49.26716613769531</v>
+        <v>49.26715469360352</v>
       </c>
       <c r="C176" t="n">
         <v>56.68000030517578</v>
@@ -5075,7 +5075,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>53.41682815551758</v>
+        <v>53.41683578491211</v>
       </c>
       <c r="C177" t="n">
         <v>61</v>
@@ -5102,7 +5102,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>50.38695907592773</v>
+        <v>50.38697052001953</v>
       </c>
       <c r="C178" t="n">
         <v>57.54000091552734</v>
@@ -5129,7 +5129,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>47.56725311279297</v>
+        <v>47.56724548339844</v>
       </c>
       <c r="C179" t="n">
         <v>54.31999969482422</v>
@@ -5156,7 +5156,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>63.26051712036133</v>
+        <v>63.26050567626953</v>
       </c>
       <c r="C180" t="n">
         <v>71.72000122070312</v>
@@ -5183,7 +5183,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>63.07526779174805</v>
+        <v>63.07527542114258</v>
       </c>
       <c r="C181" t="n">
         <v>71.51000213623047</v>
@@ -5210,7 +5210,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>58.85908889770508</v>
+        <v>58.85908508300781</v>
       </c>
       <c r="C182" t="n">
         <v>66.73000335693359</v>
@@ -5291,7 +5291,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>73.87348937988281</v>
+        <v>73.87349700927734</v>
       </c>
       <c r="C185" t="n">
         <v>83.23999786376953</v>
@@ -5318,7 +5318,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>79.20201110839844</v>
+        <v>79.20201873779297</v>
       </c>
       <c r="C186" t="n">
         <v>88.70999908447266</v>
@@ -5372,7 +5372,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>77.63065338134766</v>
+        <v>77.63066101074219</v>
       </c>
       <c r="C188" t="n">
         <v>86.94999694824219</v>
@@ -5401,7 +5401,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>76.12960052490234</v>
+        <v>76.12959289550781</v>
       </c>
       <c r="C189" t="n">
         <v>84.76000213623047</v>
@@ -5430,7 +5430,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>77.20741271972656</v>
+        <v>77.2073974609375</v>
       </c>
       <c r="C190" t="n">
         <v>85.95999908447266</v>
@@ -5459,7 +5459,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>79.8121337890625</v>
+        <v>79.81212615966797</v>
       </c>
       <c r="C191" t="n">
         <v>88.86000061035156</v>
@@ -5546,7 +5546,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>81.48188781738281</v>
+        <v>81.48189544677734</v>
       </c>
       <c r="C194" t="n">
         <v>90.19000244140625</v>
@@ -5575,7 +5575,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>93.29987335205078</v>
+        <v>93.29986572265625</v>
       </c>
       <c r="C195" t="n">
         <v>102.6999969482422</v>
@@ -5604,7 +5604,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>90.00214385986328</v>
+        <v>90.00213623046875</v>
       </c>
       <c r="C196" t="n">
         <v>99.06999969482422</v>
@@ -5633,7 +5633,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>86.22290802001953</v>
+        <v>86.22289276123047</v>
       </c>
       <c r="C197" t="n">
         <v>94.91000366210938</v>
@@ -5662,7 +5662,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>86.92993927001953</v>
+        <v>86.92994689941406</v>
       </c>
       <c r="C198" t="n">
         <v>95.12000274658203</v>
@@ -5691,7 +5691,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>87.83470153808594</v>
+        <v>87.83470916748047</v>
       </c>
       <c r="C199" t="n">
         <v>96.11000061035156</v>
@@ -5778,7 +5778,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>75.24736022949219</v>
+        <v>75.24733734130859</v>
       </c>
       <c r="C202" t="n">
         <v>81.86000061035156</v>
@@ -5807,7 +5807,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>87.16043090820312</v>
+        <v>87.16043853759766</v>
       </c>
       <c r="C203" t="n">
         <v>94.81999969482422</v>
@@ -5836,7 +5836,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>91.27748870849609</v>
+        <v>91.27747344970703</v>
       </c>
       <c r="C204" t="n">
         <v>98.72000122070312</v>
@@ -5865,7 +5865,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>93.31163024902344</v>
+        <v>93.31161499023438</v>
       </c>
       <c r="C205" t="n">
         <v>100.9199981689453</v>
@@ -5894,7 +5894,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>92.32227325439453</v>
+        <v>92.32228851318359</v>
       </c>
       <c r="C206" t="n">
         <v>99.84999847412109</v>
@@ -5923,7 +5923,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>91.19397735595703</v>
+        <v>91.19398498535156</v>
       </c>
       <c r="C207" t="n">
         <v>98.08999633789062</v>
@@ -5952,7 +5952,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>91.04524230957031</v>
+        <v>91.04524993896484</v>
       </c>
       <c r="C208" t="n">
         <v>97.93000030517578</v>
@@ -5981,7 +5981,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>92.87673187255859</v>
+        <v>92.87674713134766</v>
       </c>
       <c r="C209" t="n">
         <v>99.90000152587891</v>
@@ -6010,7 +6010,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>86.18887329101562</v>
+        <v>86.18886566162109</v>
       </c>
       <c r="C210" t="n">
         <v>92.13999938964844</v>
@@ -6068,7 +6068,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>82.25078582763672</v>
+        <v>82.25079345703125</v>
       </c>
       <c r="C212" t="n">
         <v>87.93000030517578</v>
@@ -6097,7 +6097,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>81.04447937011719</v>
+        <v>81.04447174072266</v>
       </c>
       <c r="C213" t="n">
         <v>86.04000091552734</v>
@@ -6126,7 +6126,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>67.79137420654297</v>
+        <v>67.7913818359375</v>
       </c>
       <c r="C214" t="n">
         <v>71.97000122070312</v>
@@ -6155,7 +6155,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>76.66446685791016</v>
+        <v>76.66445922851562</v>
       </c>
       <c r="C215" t="n">
         <v>81.38999938964844</v>
@@ -6184,7 +6184,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>77.31498718261719</v>
+        <v>77.31497955322266</v>
       </c>
       <c r="C216" t="n">
         <v>81.48000335693359</v>
@@ -6242,7 +6242,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>86.46221160888672</v>
+        <v>86.46220397949219</v>
       </c>
       <c r="C218" t="n">
         <v>91.12000274658203</v>
@@ -6271,7 +6271,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>85.646484375</v>
+        <v>85.64647674560547</v>
       </c>
       <c r="C219" t="n">
         <v>89.66999816894531</v>
@@ -6300,7 +6300,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>93.15380096435547</v>
+        <v>93.15379333496094</v>
       </c>
       <c r="C220" t="n">
         <v>97.52999877929688</v>
@@ -6329,7 +6329,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>96.96475982666016</v>
+        <v>96.96476745605469</v>
       </c>
       <c r="C221" t="n">
         <v>101.5199966430664</v>
@@ -6358,7 +6358,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>103.5920257568359</v>
+        <v>103.5920104980469</v>
       </c>
       <c r="C222" t="n">
         <v>107.8099975585938</v>
@@ -6387,7 +6387,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>96.46232604980469</v>
+        <v>96.46233367919922</v>
       </c>
       <c r="C223" t="n">
         <v>100.3899993896484</v>
@@ -6416,7 +6416,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>112.8932876586914</v>
+        <v>112.8932952880859</v>
       </c>
       <c r="C224" t="n">
         <v>117.4899978637695</v>
@@ -6445,7 +6445,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>119.1486206054688</v>
+        <v>119.1486282348633</v>
       </c>
       <c r="C225" t="n">
         <v>123.3399963378906</v>
@@ -6474,7 +6474,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>117.0427017211914</v>
+        <v>117.0426864624023</v>
       </c>
       <c r="C226" t="n">
         <v>121.1600036621094</v>
@@ -6503,7 +6503,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>116.8784713745117</v>
+        <v>116.8784637451172</v>
       </c>
       <c r="C227" t="n">
         <v>120.9899978637695</v>
@@ -6532,7 +6532,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>118.3167266845703</v>
+        <v>118.3167419433594</v>
       </c>
       <c r="C228" t="n">
         <v>121.8300018310547</v>
@@ -6590,7 +6590,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>125.2314147949219</v>
+        <v>125.2313995361328</v>
       </c>
       <c r="C230" t="n">
         <v>128.9499969482422</v>
@@ -6677,7 +6677,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>123.1126708984375</v>
+        <v>123.112678527832</v>
       </c>
       <c r="C233" t="n">
         <v>126.129997253418</v>
@@ -6793,7 +6793,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>156.2803649902344</v>
+        <v>156.2803497314453</v>
       </c>
       <c r="C237" t="n">
         <v>158.6000061035156</v>
@@ -6938,7 +6938,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>198.7737731933594</v>
+        <v>198.7737579345703</v>
       </c>
       <c r="C242" t="n">
         <v>200.9299926757812</v>
